--- a/HW06/testcases/23127184_HW06_TestCases.xlsx
+++ b/HW06/testcases/23127184_HW06_TestCases.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,12 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +70,13 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -89,11 +98,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +127,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,8 +598,12 @@
           <t>Pool A</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" s="4">
         <f>D5+E5</f>
         <v/>
@@ -711,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -822,7 +858,6895 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-001</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Registration succeeds with a valid name</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>200 with {message, id}</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-002</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Missing name field is rejected</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 makes name mandatory</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-003</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Null name is rejected</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>{"name": null, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-004</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Empty name is rejected</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-005</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Whitespace-only name is rejected</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "     ", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>4xx - whitespace is not a name</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="8" t="inlineStr"/>
+      <c r="L8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-006</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Single-character name is accepted</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>200 - FR-01 sets no minimum length</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: FR-01 does not state a minimum name length; treated as valid.</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-007</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Name with Vietnamese diacritics is accepted and preserved</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Lê Phạm Kiều Duyên", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>200, name stored unchanged</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr"/>
+      <c r="L10" s="8" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-008</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>255-character name is handled without error</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "NNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNN", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>200 or a 4xx limit error, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: FR-01 states no maximum length; the only firm expectation is no 5xx.</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-009</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Oversized name does not crash the server</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "NNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNN</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>4xx limit error or 200, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: No documented maximum; asserted only that the server stays healthy.</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-010</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Numeric name is rejected</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>{"name": 12345, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>4xx - name is specified as a string</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-011</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Object as name is rejected</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>{"name": {"first": "Nguyen"}, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-012</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Name with leading and trailing spaces is trimmed or rejected</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "   Nguyen Van A   ", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>200 with the value trimmed, or a 4xx; never stored padded</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: Spec is silent on trimming; recorded as a gap rather than guessed.</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-013</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Name containing emoji is handled without corruption</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Duyên 🌸 QA", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>200 or 4xx, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-014</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Registration succeeds with a well-formed email</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-015</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Missing email field is rejected</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 makes email mandatory</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-016</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Null email is rejected</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": null, "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-017</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Empty email is rejected</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr"/>
+      <c r="K20" s="8" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr"/>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-018</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Whitespace-only email is rejected</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "    ", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-019</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Email without '@' is rejected</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 requires the user@domain.com form</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-020</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Email with nothing after '@' is rejected</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-021</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Email with nothing before '@' is rejected</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-022</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Email without a TLD is rejected</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>4xx - user@domain.com form required</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-023</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Email with a duplicated '@' is rejected</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-024</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Email starting with a dot is rejected</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": ".{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-025</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Email with a dot immediately before '@' is rejected</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}.@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-026</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Email with consecutive dots is rejected</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "us..er{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-027</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Email containing a space is rejected</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "us er{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-028</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Email with parentheses in the local part is rejected</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "us()er{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-029</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Email with a '+' tag is accepted</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}+qa@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>200 - valid per RFC 5322</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-030</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Email on a subdomain is accepted</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@mail.domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-031</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Email on a hyphenated domain is accepted</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@my-shop.com.vn", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr"/>
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-032</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Email in uppercase is accepted</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniqUpper}}@DOMAIN.COM", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>200 - the local part is case-preserving, the domain case-insensitive</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-033</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Registering an email that already exists is rejected</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "dup{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01: email must be "duy nhất trong hệ thống"</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-034</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Uniqueness is enforced case-insensitively</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "DUP{{uniq}}@DOMAIN.COM", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>4xx - email addresses differing only in case are the same account</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-035</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Over-long email local part is rejected</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>4xx - RFC 5321 caps the local part at 64 characters</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr"/>
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-036</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Numeric email is rejected</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": 12345, "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-037</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Email with a trailing space is trimmed or rejected</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com ", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>200 with the value trimmed, or 4xx; never stored with the space</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: Spec does not say whether inputs are trimmed.</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-038</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Registration succeeds with a compliant password</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-039</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Missing password field is rejected</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com"}</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-040</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Null password is rejected</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": null}</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-041</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Empty password is rejected</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": ""}</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-042</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Seven-character password is rejected</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass12!"}</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 requires at least 8 characters</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-043</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Eight-character compliant password is accepted</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass123!"}</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>200 - exactly at the minimum</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-044</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Nine-character compliant password is accepted</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass1234!"}</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-045</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Password without an uppercase letter is rejected</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password123!"}</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-046</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Password without a lowercase letter is rejected</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "PASSWORD123!"}</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr"/>
+      <c r="M49" s="8" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-047</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Password without a digit is rejected</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password!!"}</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-048</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Password without a special character is rejected</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123"}</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr"/>
+      <c r="M51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-049</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Password whose only special character is '#' is rejected</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123#"}</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 permits only @ $ ! % * ? &amp;</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr"/>
+      <c r="K52" s="8" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr"/>
+      <c r="N52" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-050</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Password using '@' (at sign) is accepted</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd@"}</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>200 - '@' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr"/>
+      <c r="M53" s="8" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-051</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Password using '$' (dollar sign) is accepted</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd$"}</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>200 - '$' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="8" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr"/>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-052</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Password using '!' (exclamation mark) is accepted</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd!"}</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>200 - '!' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr"/>
+      <c r="K55" s="8" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr"/>
+      <c r="M55" s="8" t="inlineStr"/>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-053</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Password using '%' (percent sign) is accepted</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd%"}</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>200 - '%' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr"/>
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+      <c r="N56" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-054</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Password using '*' (asterisk) is accepted</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd*"}</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>200 - '*' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr"/>
+      <c r="K57" s="8" t="inlineStr"/>
+      <c r="L57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-055</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Password using '?' (question mark) is accepted</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd?"}</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>200 - '?' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-056</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Password using '&amp;' (ampersand) is accepted</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd&amp;"}</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>200 - '&amp;' is in the FR-01 permitted set</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr"/>
+      <c r="K59" s="8" t="inlineStr"/>
+      <c r="L59" s="8" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-057</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>All-numeric password is rejected</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "12345678"}</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>4xx - no letters, no special character</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-058</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>All-alphabetic password is rejected</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passwordd"}</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>4xx - no digit, no special character</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr"/>
+      <c r="K61" s="8" t="inlineStr"/>
+      <c r="L61" s="8" t="inlineStr"/>
+      <c r="M61" s="8" t="inlineStr"/>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-059</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Whitespace-only password is rejected</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "        "}</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-060</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>A weak but non-compliant password like 'password' is rejected</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password"}</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>4xx - fails three complexity rules</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-061</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Password containing a space is handled consistently</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass 123!"}</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>200 - FR-01 does not forbid spaces; must not 5xx</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: FR-01 neither permits nor forbids whitespace inside a password.</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-062</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Very long password does not crash the server</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Aa1!xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>200 or 4xx, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: No documented maximum length.</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr"/>
+      <c r="M65" s="8" t="inlineStr"/>
+      <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O65" s="8" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-063</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Numeric password is rejected</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": 12345678}</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-064</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Password containing non-ASCII characters is handled without corruption</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Mật khẩu1!"}</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>200 or 4xx, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="inlineStr"/>
+      <c r="M67" s="8" t="inlineStr"/>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-065</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Registration succeeds when the password confirmation matches</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: Field required by FR-01 but absent from api_specification.md.</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-066</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Mismatched password confirmation is rejected</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password456!"}</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>4xx - FR-01: "hệ thống từ chối nếu hai trường không khớp"</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr"/>
+      <c r="M69" s="8" t="inlineStr"/>
+      <c r="N69" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-067</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Missing password confirmation is rejected</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>4xx - FR-01 makes the confirmation field mandatory</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: Tests FR-01 against a spec that omits the field - expect disagreement.</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-068</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Empty request body is rejected</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>4xx - all three fields are mandatory</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-069</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Request with no body is rejected</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr"/>
+      <c r="L72" s="8" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-070</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Malformed JSON is rejected with a 400, not a 500</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"name": "Broken", "email": "{{uniq}}@domain.com", </t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>400 - a parse failure is a client error</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-071</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Non-JSON Content-Type is rejected</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>name=Test&amp;email=a@b.com&amp;password=Password123!</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>400 or 415 - the endpoint is documented as JSON</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-072</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Array request body is rejected</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>[{"name": "A", "email": "a@b.com", "password": "Password123!"}]</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr"/>
+      <c r="L75" s="8" t="inlineStr"/>
+      <c r="M75" s="8" t="inlineStr"/>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-073</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Unknown extra fields are ignored, not stored</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "nickname": "duyen", "favouriteColour": "pink"}</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>200 - undocumented fields are ignored</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-074</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>All-null request body is rejected</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>{"name": null, "email": null, "password": null}</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>4xx</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-075</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Oversized payload is refused without a server error</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "NNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNN</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>400 or 413, never a 5xx</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: No documented payload limit.</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="inlineStr"/>
+      <c r="M78" s="8" t="inlineStr"/>
+      <c r="N78" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-076</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/register is not routed</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/register</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>404 or 405 - the spec documents POST only</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-077</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>PUT /api/register is not routed</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>PUT /api/register</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>404 or 405 - the spec documents POST only</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-078</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>DELETE /api/register is not routed</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>DELETE /api/register</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>404 or 405 - the spec documents POST only</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O81" s="8" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>A1-DP-079</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>PATCH /api/register is not routed</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>PATCH /api/register</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>404 or 405 - the spec documents POST only</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-001</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-02</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>A newly registered account can immediately log in</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>200 with a JWT - registration leaves the account usable</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr"/>
+      <c r="L83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-002</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>A duplicate registration does not replace the existing account</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>200 - the original password still works; the duplicate changed nothing</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-003</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-04</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>The registered account's profile is retrievable after login</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/users/me</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>200 and the profile matches the registered email</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="inlineStr"/>
+      <c r="M85" s="8" t="inlineStr"/>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-004</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / SEC-03</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>A newly registered account starts with role 'user'</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/users/me</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>role is exactly 'user' - registration never grants admin</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr"/>
+      <c r="L86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-005</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-02</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>A newly registered account is not locked and has zero failed attempts</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/users/me</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>login_attempts = 0 and locked_until is null</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr"/>
+      <c r="L87" s="8" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-006</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-03</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Password reset can be initiated for a newly registered account</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/forgot-password</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}"}</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>200 - the account exists, so a reset token is issued</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-007</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Consecutive registrations receive distinct, increasing ids</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "second{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>200 and an id strictly greater than the fixture account's id</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="8" t="inlineStr"/>
+      <c r="M89" s="8" t="inlineStr"/>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-008</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>A registration rejected for an invalid email leaves no usable account</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "bad{{uniq}}", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>401 - no account was created, so login must fail</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-009</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-07</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>A newly registered account starts with an empty cart</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/cart</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>200 with an empty array</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>A1-ST-010</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>FR-01 / FR-11</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>A newly registered account has no orders</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/orders/my-orders</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>200 with an empty array</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O92" s="8" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-001</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>The login response must not disclose the stored password</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>no password field, and certainly not the plaintext just submitted</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="inlineStr"/>
+      <c r="M93" s="8" t="inlineStr"/>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-002</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>The registration response must not echo the password</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>the response body contains neither the password nor a password field</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O94" s="8" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-003</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>The profile endpoint must not expose the password</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/users/me</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>no password field in the profile payload</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+      <c r="N95" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-004</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>The stored password must not equal the submitted plaintext</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>if any password material is returned it must look hashed, not plaintext</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+      <c r="N96" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-005</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>SEC-04</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>A script payload in the name is stored as inert data</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/users/me</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>returned as a JSON string, with Content-Type application/json</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
+      <c r="N97" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-006</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>SEC-04</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>An onerror payload in the name is stored without a server error</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "&lt;img src=x onerror=alert(1)&gt;", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>handled as data; no 5xx and no HTML content type</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-007</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>A DROP TABLE payload in the email must be neutralised</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sqli{{uniq}}'); DROP TABLE users;--@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>rejected or stored literally; never a 5xx, never a SQL error</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr"/>
+      <c r="M99" s="8" t="inlineStr"/>
+      <c r="N99" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-008</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>An OR 1=1 payload in the name must be neutralised</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "' OR '1'='1", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>stored literally; never a 5xx, never a SQL error</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr"/>
+      <c r="M100" s="8" t="inlineStr"/>
+      <c r="N100" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-009</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>A UNION SELECT payload must not return extra data</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "u{{uniq}}' UNION SELECT id,email,password FROM users--@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>no 5xx, no leaked rows, no SQL error text</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr"/>
+      <c r="L101" s="8" t="inlineStr"/>
+      <c r="M101" s="8" t="inlineStr"/>
+      <c r="N101" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O101" s="8" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-010</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>A comment-sequence payload in the password must be neutralised</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Aa1!'--"}</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>no 5xx, no SQL error text</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr"/>
+      <c r="M102" s="8" t="inlineStr"/>
+      <c r="N102" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-011</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>The users table survives the injection attempts intact</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{admin_email}}", "password": "{{admin_password}}"}</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>200 - the seeded admin account is still there and still works</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr"/>
+      <c r="M103" s="8" t="inlineStr"/>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-012</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>A client-supplied role must not create an admin account</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>the account's role is 'user' - the injected value was ignored</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-013</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>An account registered with an injected role cannot reach admin APIs</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/admin/users</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>401 or 403 - SEC-03 requires a genuine admin role</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr"/>
+      <c r="M105" s="8" t="inlineStr"/>
+      <c r="N105" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-014</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>A client-supplied id must not override the generated one</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "idinj{{uniq}}@domain.com", "password": "Password123!", "id": 1}</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>200 with a server-generated id that is not the injected 1</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr"/>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-015</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Injected lockout fields must not affect the new account</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/login</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "{{stEmail}}", "password": "{{stPassword}}"}</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>200 - the injected lock was ignored, so login still works</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr"/>
+      <c r="L107" s="8" t="inlineStr"/>
+      <c r="M107" s="8" t="inlineStr"/>
+      <c r="N107" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O107" s="8" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-016</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06 / SEC-07</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>A client-supplied reset token must not be usable</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/reset-password</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>{"email": "rst{{uniq}}@domain.com", "resetToken": "123456", "newPassword": "Hijacked999!"}</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>4xx - a token the client chose must never authorise a reset</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O108" s="8" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-017</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>SEC-06</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>A __proto__ payload does not crash or escalate</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>{"name":"Proto Probe","email":"proto{{uniq}}@domain.com","password":"Password123!","__proto__":{"role":"admin"}}</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>no 5xx; the payload is ignored</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr"/>
+      <c r="L109" s="8" t="inlineStr"/>
+      <c r="M109" s="8" t="inlineStr"/>
+      <c r="N109" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O109" s="8" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-018</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Registration must not return an authentication token</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "tok{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>no token/JWT in the response - FR-01 sends the user to the login page</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr"/>
+      <c r="K110" s="8" t="inlineStr"/>
+      <c r="L110" s="8" t="inlineStr"/>
+      <c r="M110" s="8" t="inlineStr"/>
+      <c r="N110" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O110" s="8" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-019</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>SEC-05</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>A failed registration must not leak database internals</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>{"name": {"nested": {"deep": true}}, "email": "err{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>a clean 4xx message with no driver, table or stack detail</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr"/>
+      <c r="L111" s="8" t="inlineStr"/>
+      <c r="M111" s="8" t="inlineStr"/>
+      <c r="N111" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O111" s="8" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>A1-SEC-020</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>SEC-02 (not applicable)</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>Registration works without any Authorization header</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "pub{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>200 - SEC-02 does not apply; registration must stay public</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J112" s="8" t="inlineStr"/>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>SPEC GAP: Documents why SEC-02 is not applicable to this endpoint.</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr"/>
+      <c r="M112" s="8" t="inlineStr"/>
+      <c r="N112" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-001</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>The success response contains exactly {message, id}</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>body validates against the spec schema with additionalProperties false</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="inlineStr"/>
+      <c r="M113" s="8" t="inlineStr"/>
+      <c r="N113" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O113" s="8" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-002</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>The success message is exactly the documented string</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch2{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>message === "User registered successfully"</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J114" s="8" t="inlineStr"/>
+      <c r="K114" s="8" t="inlineStr"/>
+      <c r="L114" s="8" t="inlineStr"/>
+      <c r="M114" s="8" t="inlineStr"/>
+      <c r="N114" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O114" s="8" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-003</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>The returned id is a JSON integer, not a string</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch3{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>typeof id === 'number' and Number.isInteger(id)</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr"/>
+      <c r="M115" s="8" t="inlineStr"/>
+      <c r="N115" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O115" s="8" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-004</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>The returned id is a positive identifier</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch4{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>id &gt; 0</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="8" t="inlineStr"/>
+      <c r="M116" s="8" t="inlineStr"/>
+      <c r="N116" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-005</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>The response is served as application/json</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch5{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>Content-Type includes application/json</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr"/>
+      <c r="M117" s="8" t="inlineStr"/>
+      <c r="N117" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-006</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>A successful registration returns HTTP 200 as documented</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch6{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>200 - the spec documents 200 OK, not 201</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr"/>
+      <c r="M118" s="8" t="inlineStr"/>
+      <c r="N118" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O118" s="8" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-007</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>A validation error returns a structured error body</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>4xx with {"error": "&lt;string&gt;"}</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr"/>
+      <c r="K119" s="8" t="inlineStr"/>
+      <c r="L119" s="8" t="inlineStr"/>
+      <c r="M119" s="8" t="inlineStr"/>
+      <c r="N119" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-008</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance / SEC-01</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>The response exposes no credential or role fields</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch8{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>no password, role, token or reset_token key anywhere in the body</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr"/>
+      <c r="L120" s="8" t="inlineStr"/>
+      <c r="M120" s="8" t="inlineStr"/>
+      <c r="N120" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O120" s="8" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-009</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>The success body carries no undocumented fields</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "sch9{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>exactly two keys: message and id</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr"/>
+      <c r="K121" s="8" t="inlineStr"/>
+      <c r="L121" s="8" t="inlineStr"/>
+      <c r="M121" s="8" t="inlineStr"/>
+      <c r="N121" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-010</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>A duplicate-email rejection returns a structured error body</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "dupsch{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>4xx with {"error": "&lt;string&gt;"} naming the conflict</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J122" s="8" t="inlineStr"/>
+      <c r="K122" s="8" t="inlineStr"/>
+      <c r="L122" s="8" t="inlineStr"/>
+      <c r="M122" s="8" t="inlineStr"/>
+      <c r="N122" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O122" s="8" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-011</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>Two registrations never return the same id</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>fixture in pre-request script</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Nguyen Van A", "email": "uniq2{{uniq}}@domain.com", "password": "Password123!"}</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>the returned id differs from the fixture account's id</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J123" s="8" t="inlineStr"/>
+      <c r="K123" s="8" t="inlineStr"/>
+      <c r="L123" s="8" t="inlineStr"/>
+      <c r="M123" s="8" t="inlineStr"/>
+      <c r="N123" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>A1-SCH-012</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>spec conformance</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>Errors are JSON, never an HTML stack-trace page</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/register</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>{"name": "Broken",</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>the error response is JSON or plain text, never an HTML error page</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>AI-generated</t>
+        </is>
+      </c>
+      <c r="J124" s="8" t="inlineStr"/>
+      <c r="K124" s="8" t="inlineStr"/>
+      <c r="L124" s="8" t="inlineStr"/>
+      <c r="M124" s="8" t="inlineStr"/>
+      <c r="N124" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O124" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B4:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -848,7 +7772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -959,7 +7883,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B4:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -985,7 +7908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1096,7 +8019,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B4:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1122,7 +8044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1233,7 +8155,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B4:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/HW06/testcases/23127184_HW06_TestCases.xlsx
+++ b/HW06/testcases/23127184_HW06_TestCases.xlsx
@@ -611,10 +611,10 @@
         <v>126</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
@@ -649,10 +649,10 @@
         <v>88</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>3</v>
@@ -687,10 +687,10 @@
         <v>94</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>5</v>
@@ -725,10 +725,10 @@
         <v>78</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>2</v>
@@ -753,10 +753,10 @@
         <v>386</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>275</v>
+        <v>386</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>16</v>
@@ -924,7 +924,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>{"email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>{"name": null, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": null, "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>{"name": "", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>{"name": "     ", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "     ", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>{"name": "A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Lê Phạm Kiều Duyên", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Lê Phạm Kiều Duyên", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>{"name": "NNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNN", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "NNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNNN", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>{"name": 12345, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": 12345, "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>{"name": {"first": "Nguyen"}, "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": {"first": "Nguyen"}, "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>{"name": "   Nguyen Van A   ", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "   Nguyen Van A   ", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Duyên 🌸 QA", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Duyên 🌸 QA", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": null, "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": null, "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "    ", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "    ", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": ".{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": ".{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}.@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}.@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "us..er{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "us..er{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O29" s="8" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "us er{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "us er{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "us()er{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "us()er{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}+qa@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}+qa@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@mail.domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@mail.domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@my-shop.com.vn", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@my-shop.com.vn", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniqUpper}}@DOMAIN.COM", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniqUpper}}@DOMAIN.COM", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "dup{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "dup{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 409; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "DUP{{uniq}}@DOMAIN.COM", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "DUP{{uniq}}@DOMAIN.COM", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 409; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O38" s="8" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": 12345, "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": 12345, "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com ", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com ", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/4 assertions passed</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": null}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": null, "confirmPassword": null}</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": ""}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "", "confirmPassword": ""}</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass12!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass12!", "confirmPassword": "Pass12!"}</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass123!", "confirmPassword": "Pass123!"}</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass1234!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass1234!", "confirmPassword": "Pass1234!"}</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password123!", "confirmPassword": "password123!"}</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "PASSWORD123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "PASSWORD123!", "confirmPassword": "PASSWORD123!"}</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O49" s="8" t="inlineStr"/>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password!!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password!!", "confirmPassword": "Password!!"}</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123", "confirmPassword": "Password123"}</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O51" s="8" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123#"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123#", "confirmPassword": "Password123#"}</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd@"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd@", "confirmPassword": "Passw0rd@"}</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd$"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd$", "confirmPassword": "Passw0rd$"}</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd!", "confirmPassword": "Passw0rd!"}</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd%"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd%", "confirmPassword": "Passw0rd%"}</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd*"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd*", "confirmPassword": "Passw0rd*"}</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd?"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd?", "confirmPassword": "Passw0rd?"}</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd&amp;"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passw0rd&amp;", "confirmPassword": "Passw0rd&amp;"}</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "12345678"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "12345678", "confirmPassword": "12345678"}</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passwordd"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Passwordd", "confirmPassword": "Passwordd"}</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "        "}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "        ", "confirmPassword": "        "}</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "password", "confirmPassword": "password"}</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass 123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Pass 123!", "confirmPassword": "Pass 123!"}</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": 12345678}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": 12345678, "confirmPassword": 12345678}</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr"/>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Mật khẩu1!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Mật khẩu1!", "confirmPassword": "Mật khẩu1!"}</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O69" s="8" t="inlineStr"/>
@@ -5772,12 +5772,12 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O70" s="8" t="inlineStr"/>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O71" s="8" t="inlineStr"/>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O72" s="8" t="inlineStr"/>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>HTTP 500; 3/5 assertions passed; expected 500 to be one of [ 400, 415 ] | status code: expected 500 to be below 500</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O74" s="8" t="inlineStr"/>
@@ -6133,12 +6133,12 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O75" s="8" t="inlineStr"/>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "nickname": "duyen", "favouriteColour": "pink"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!", "nickname": "duyen", "favouriteColour": "pink"}</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>{"name": null, "email": null, "password": null}</t>
+          <t>{"name": null, "email": null, "password": null, "confirmPassword": null}</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr"/>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "second{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "second{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected 200 to be one of [ 400, 401, 404 ]</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O90" s="8" t="inlineStr"/>
@@ -7411,12 +7411,12 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; user object: expected { id: 92, name: 'State Fixture', …(8) } to not have property 'password' | expected 'Password123!' to not deeply equal 'Password123!'</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O93" s="8" t="inlineStr"/>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected { id: 94, name: 'State Fixture', …(8) } to not have property 'password'</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N95" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O95" s="8" t="inlineStr"/>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected 'Password123!' to not deeply equal 'Password123!'</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O96" s="8" t="inlineStr"/>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>{"name": "&lt;img src=x onerror=alert(1)&gt;", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "&lt;img src=x onerror=alert(1)&gt;", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sqli{{uniq}}'); DROP TABLE users;--@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sqli{{uniq}}'); DROP TABLE users;--@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N99" s="8" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>{"name": "' OR '1'='1", "email": "{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "' OR '1'='1", "email": "{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "u{{uniq}}' UNION SELECT id,email,password FROM users--@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "u{{uniq}}' UNION SELECT id,email,password FROM users--@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 6/6 assertions passed</t>
+          <t>HTTP 400; 6/6 assertions passed</t>
         </is>
       </c>
       <c r="N101" s="8" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Aa1!'--"}</t>
+          <t>{"name": "Nguyen Van A", "email": "{{uniq}}@domain.com", "password": "Aa1!'--", "confirmPassword": "Aa1!'--"}</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected 200 to be one of [ 401, 403 ]</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N105" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O105" s="8" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "idinj{{uniq}}@domain.com", "password": "Password123!", "id": 1}</t>
+          <t>{"name": "Nguyen Van A", "email": "idinj{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!", "id": 1}</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N109" s="8" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "tok{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "tok{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>{"name": {"nested": {"deep": true}}, "email": "err{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": {"nested": {"deep": true}}, "email": "err{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N111" s="8" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "pub{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "pub{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch2{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch2{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch3{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch3{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch4{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch4{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch5{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch5{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch6{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch6{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected 200 to be within 400..499 | expected { …(2) } to have property 'error'</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N119" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O119" s="8" t="inlineStr"/>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch8{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch8{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "sch9{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "sch9{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "dupsch{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "dupsch{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected 200 to be within 400..499 | expected { …(2) } to have property 'error'</t>
+          <t>HTTP 409; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr"/>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "uniq2{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "uniq2{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>HTTP 400; 3/5 assertions passed; expected 'text/html; charset=utf-8' to not include 'text/html' | expected '&lt;!doctype html&gt;\n&lt;html lang="en"&gt;\n&lt;h…' to not include '&lt;pre&gt;'</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr"/>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "tab{{uniq}}\t@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "tab{{uniq}}\t@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N125" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O125" s="8" t="inlineStr"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen Van A", "email": "crlf{{uniq}}\r\nX-Injected: yes@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen Van A", "email": "crlf{{uniq}}\r\nX-Injected: yes@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 6/7 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N126" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O126" s="8" t="inlineStr"/>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyen\u0000Van A", "email": "nul{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyen\u0000Van A", "email": "nul{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 6/7 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N127" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O127" s="8" t="inlineStr"/>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>{"name": "Nguyễn Văn A", "email": "charset{{uniq}}@domain.com", "password": "Password123!"}</t>
+          <t>{"name": "Nguyễn Văn A", "email": "charset{{uniq}}@domain.com", "password": "Password123!", "confirmPassword": "Password123!"}</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N129" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O129" s="8" t="inlineStr"/>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected response to have status code 404 but got 200 | 200 with {} makes "missing" indistinguishable from "blank": expected true to be false</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr"/>
@@ -10715,12 +10715,12 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected response to have status code 404 but got 200 | 200 with {} makes "missing" indistinguishable from "blank": expected true to be false</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr"/>
@@ -10784,12 +10784,12 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected response to have status code 404 but got 200 | 200 with {} makes "missing" indistinguishable from "blank": expected true to be false</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr"/>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr"/>
@@ -10922,12 +10922,12 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr"/>
@@ -10991,12 +10991,12 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/6 assertions passed; expected response to have status code 404 but got 200 | 200 with {} makes "missing" indistinguishable from "blank": expected true to be false</t>
+          <t>HTTP 404; 6/6 assertions passed</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr"/>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr"/>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr"/>
@@ -11336,12 +11336,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr"/>
@@ -11405,12 +11405,12 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr"/>
@@ -11474,12 +11474,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr"/>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr"/>
@@ -11612,12 +11612,12 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr"/>
@@ -11681,12 +11681,12 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr"/>
@@ -11750,12 +11750,12 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr"/>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr"/>
@@ -11888,12 +11888,12 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr"/>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/4 assertions passed</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/4 assertions passed</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
@@ -12785,12 +12785,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; expected '222000' to be a number</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
@@ -12854,12 +12854,12 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected response to have status code 404 but got 200 | 200 with {} makes "missing" indistinguishable from "blank": expected true to be false</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr"/>
@@ -12992,12 +12992,12 @@
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected { id: 2, …(5) } to deeply equal { id: 2, …(5) } | detail price type: expected 'string' to deeply equal 'number'</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr"/>
@@ -13268,12 +13268,12 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; id 14 returned price as string: expected '999000' to be a number</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 7/7 assertions passed</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 7/7 assertions passed</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 7/7 assertions passed</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 7/7 assertions passed</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 7/7 assertions passed</t>
+          <t>HTTP 400; 7/7 assertions passed</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 6/6 assertions passed</t>
+          <t>HTTP 400; 6/6 assertions passed</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="M59" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -14104,12 +14104,12 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -14173,12 +14173,12 @@
       </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -14246,12 +14246,12 @@
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
@@ -14315,12 +14315,12 @@
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr"/>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/5 assertions passed</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
@@ -14522,13 +14522,12 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected data to satisfy schema but found following errors: 
-data.price should be number</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr"/>
@@ -14661,13 +14660,12 @@
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected data to satisfy schema but found following errors: 
-data.price should be number</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O68" s="8" t="inlineStr"/>
@@ -14869,12 +14867,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; product 2 returned price as a string: expected '28000000' to be a number | adding 1 must not concatenate: expected '280000001' to deeply equal 28000001</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O71" s="8" t="inlineStr"/>
@@ -15007,12 +15005,12 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; product 4 returned price as a string: expected '6000000' to be a number | adding 1 must not concatenate: expected '60000001' to deeply equal 6000001</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O73" s="8" t="inlineStr"/>
@@ -15628,12 +15626,12 @@
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected response to have status code 404 but got 200 | expected {} to have property 'error'</t>
+          <t>HTTP 404; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O82" s="8" t="inlineStr"/>
@@ -15904,7 +15902,7 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/4 assertions passed</t>
+          <t>HTTP 404; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
@@ -16180,12 +16178,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 5/6 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 6/6 assertions passed</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O90" s="8" t="inlineStr"/>
@@ -16249,12 +16247,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O91" s="8" t="inlineStr"/>
@@ -17006,12 +17004,12 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr"/>
@@ -19007,12 +19005,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
@@ -19871,12 +19869,12 @@
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr"/>
@@ -20224,12 +20222,12 @@
       </c>
       <c r="M58" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..404</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr"/>
@@ -20293,12 +20291,12 @@
       </c>
       <c r="M59" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..404</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -20362,12 +20360,12 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..404</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -20431,12 +20429,12 @@
       </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; expected '{"id":39,"user_id":183,"total_amount"…' to not include '99 Secret Lane'</t>
+          <t>HTTP 401; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
@@ -20707,12 +20705,12 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O65" s="8" t="inlineStr"/>
@@ -20780,12 +20778,12 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; status code: expected 200 to be within 401..403 | a 200 here means the role claim was never checked: expected 200 to not deeply equal 200</t>
+          <t>HTTP 403; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr"/>
@@ -22643,12 +22641,12 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 4/5 assertions passed; expected 'canceled' to deeply equal 'shipping'</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O93" s="8" t="inlineStr"/>
@@ -23607,12 +23605,12 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr"/>
@@ -25437,12 +25435,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 400..499</t>
+          <t>HTTP 400; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
@@ -25940,12 +25938,12 @@
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr"/>
@@ -26009,12 +26007,12 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr"/>
@@ -26220,12 +26218,12 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr"/>
@@ -26289,12 +26287,12 @@
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O49" s="8" t="inlineStr"/>
@@ -26358,12 +26356,12 @@
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; status code: expected 200 to be within 401..403</t>
+          <t>HTTP 403; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr"/>
@@ -27072,12 +27070,12 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/4 assertions passed; a customer must not be able to mark their own order delivered: expected 'delivered' to deeply equal 'shipping'</t>
+          <t>HTTP 200; 4/4 assertions passed</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr"/>
@@ -27831,12 +27829,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected 200 to be one of [ 401, 403 ] | expected [ …(100) ] to have property 'error'</t>
+          <t>HTTP 403; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O71" s="8" t="inlineStr"/>
@@ -28460,12 +28458,12 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200; 3/5 assertions passed; expected 200 to be one of [ 401, 403 ] | expected 'shipping' to deeply equal 'confirmed'</t>
+          <t>HTTP 200; 5/5 assertions passed</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="O80" s="8" t="inlineStr"/>
